--- a/out/Attention-MambaAMT_repeat_2_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.382453332183273</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-3.171991106271274</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-3.171991106271274</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.571991106271275</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.382453332183273</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-3.171991106271274</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.382453332183273</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.382453332183273</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-3.171991106271274</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-0.0004499999204052146</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.5791847404061293</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>1.159465998829599</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.133757660132265</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.171991106271274</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.382453332183273</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001827941945047351</v>
+        <v>0.4443803962051235</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5615832982950103</v>
+        <v>1.833142748163078</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.571991106271275</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.124102046000123</v>
+        <v>4.11431610819953</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1074525743059096</v>
+        <v>0.3507512096434337</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9824533321832729</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7766044997629491</v>
+        <v>2.980000666234655</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1882135920303203</v>
+        <v>0.6143740082650746</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.04563165781067</v>
+        <v>3.858169408666996</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1030726122005352</v>
+        <v>0.3364535643620947</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.063401061437282</v>
+        <v>3.916172975852533</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04257029310355143</v>
+        <v>0.1389602219514902</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.045361377214131</v>
+        <v>3.857287147178575</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05303893207060721</v>
+        <v>0.1731320213686761</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.108876681584524</v>
+        <v>4.064615273471765</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03193687886334741</v>
+        <v>0.1042478407368316</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.119674533559281</v>
+        <v>4.099861646975579</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02428061347147429</v>
+        <v>0.07925728174293133</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.13628523461985</v>
+        <v>4.154082641657277</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01073702507113432</v>
+        <v>0.03505490758412869</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.133460405360304</v>
+        <v>4.144866861687584</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008520075928797678</v>
+        <v>0.02781633314784061</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.139758848433499</v>
+        <v>4.165432929567436</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004222501644985529</v>
+        <v>0.01379316513239064</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.139678398021317</v>
+        <v>4.165181645808851</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002453274630056962</v>
+        <v>0.008018575656446274</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.140360212769143</v>
+        <v>4.167418752332209</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001222682714655666</v>
+        <v>0.004006787828223137</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.140353684221288</v>
+        <v>4.167408757385546</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006015507622625393</v>
+        <v>0.001978507232043375</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.140333295403909</v>
+        <v>4.167353546892345</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003487911944576901</v>
+        <v>0.001146490208376444</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.140426131799674</v>
+        <v>4.167666976671015</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001132944160405111</v>
+        <v>0.0003788988596031681</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.140303639775085</v>
+        <v>4.167279574787687</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.339056982904712e-05</v>
+        <v>0.0001881380386653097</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.140299299717237</v>
+        <v>4.167276725740255</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.680054969141058e-05</v>
+        <v>0.0001001864335946658</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.140299677296279</v>
+        <v>4.167289050088415</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>4.714396983319175e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.140293590976268</v>
+        <v>4.167280635939809</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>2.700120820192495e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.140292357785115</v>
+        <v>4.167287468789948</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.140286022924568</v>
+        <v>4.167278799535257</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>3.872723086529542e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.140281780314414</v>
+        <v>4.167276071704795</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.140282008635449</v>
+        <v>4.167271752713646</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.140282098580099</v>
+        <v>4.167266928540757</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.140281240646514</v>
+        <v>4.167266070607172</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.140281468967549</v>
+        <v>4.167266298928207</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.140280673303337</v>
+        <v>4.167265503263995</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.14028073557271</v>
+        <v>4.167265565533368</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.140280763247987</v>
+        <v>4.167265593208644</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.14028091546201</v>
+        <v>4.167265745422668</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.140280569521049</v>
+        <v>4.167265399481706</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.14028064562806</v>
+        <v>4.167265475588717</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.140280811679722</v>
+        <v>4.167265641640379</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.140281171458322</v>
+        <v>4.16726600141898</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.14028119221478</v>
+        <v>4.167266022175437</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.140281295997068</v>
+        <v>4.167266125957726</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.140281524318103</v>
+        <v>4.16726635427876</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.140281399779357</v>
+        <v>4.167266229740014</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.140281427454634</v>
+        <v>4.167266257415291</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.140281482805187</v>
+        <v>4.167266312765845</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.140281745720318</v>
+        <v>4.167266575680975</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.140281662694487</v>
+        <v>4.167266492655145</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.14028145512991</v>
+        <v>4.167266285090569</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.140281468967549</v>
+        <v>4.167266298928207</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.140281607343933</v>
+        <v>4.16726643730459</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.140281323672345</v>
+        <v>4.167266153633003</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.140281150701864</v>
+        <v>4.167265980662522</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.140281046919576</v>
+        <v>4.167265876880233</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.14028119221478</v>
+        <v>4.167266022175437</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.140281434373453</v>
+        <v>4.167266264334111</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.140281261402972</v>
+        <v>4.167266091363629</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.140280963893745</v>
+        <v>4.167265793854402</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.140280950056106</v>
+        <v>4.167265780016765</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.140280583358687</v>
+        <v>4.167265413319345</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.140280583358687</v>
+        <v>4.167265413319345</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.140280521089314</v>
+        <v>4.167265351049972</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.140280417307025</v>
+        <v>4.167265247267683</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.140280244336545</v>
+        <v>4.167265074297203</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.140280292768279</v>
+        <v>4.167265122728938</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.140279932989679</v>
+        <v>4.167264762950337</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.140279891476764</v>
+        <v>4.167264721437421</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.140279946827317</v>
+        <v>4.167264776787976</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.140280002177872</v>
+        <v>4.167264832138529</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.571991106271275</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.140280043690787</v>
+        <v>4.167264873651445</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.140279773856837</v>
+        <v>4.167264603817495</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.140279829207391</v>
+        <v>4.167264659168048</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.140279974502595</v>
+        <v>4.167264804463253</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.140279939908498</v>
+        <v>4.167264769869156</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.14027992607086</v>
+        <v>4.167264756031518</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.14028001601551</v>
+        <v>4.167264845976168</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.140280334281194</v>
+        <v>4.167265164241853</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.140280154391895</v>
+        <v>4.167264984352553</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.14028019590481</v>
+        <v>4.167265025865468</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.140280009096691</v>
+        <v>4.167264839057348</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.140280078284883</v>
+        <v>4.167264908245541</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.140279877639126</v>
+        <v>4.167264707599784</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.140279919152041</v>
+        <v>4.167264749112698</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.140279946827317</v>
+        <v>4.167264776787976</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.382453332183273</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-3.171991106271274</v>
+        <v>-2.009365330014588</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.571991106271275</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-3.171991106271274</v>
+        <v>-2.009365330014588</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001827941945047351</v>
+        <v>-6.759903522219975e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5615832982950103</v>
+        <v>0.20767885579996</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.571991106271275</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.124102046000123</v>
+        <v>0.4157036497069443</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1074525743059096</v>
+        <v>0.0397369469071638</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9824533321832729</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7766044997629491</v>
+        <v>0.2871957454408463</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1882135920303203</v>
+        <v>0.06960303108402328</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.04563165781067</v>
+        <v>0.3866846507943839</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1030726122005352</v>
+        <v>0.03811715271737443</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.063401061437282</v>
+        <v>0.3932559730507666</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04257029310355143</v>
+        <v>0.01574293918332445</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.045361377214131</v>
+        <v>0.3865846570162738</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05303893207060721</v>
+        <v>0.01961484167448919</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.108876681584524</v>
+        <v>0.4100736500071681</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03193687886334741</v>
+        <v>0.01180953426079297</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.119674533559281</v>
+        <v>0.4140657003616435</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02428061347147429</v>
+        <v>0.00897624121768067</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.13628523461985</v>
+        <v>0.4202064088120279</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01073702507113432</v>
+        <v>0.003968230163905284</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.133460405360304</v>
+        <v>0.4191584950322642</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008520075928797678</v>
+        <v>0.003147764766567189</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.139758848433499</v>
+        <v>0.4214846500149544</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004222501644985529</v>
+        <v>0.001558425164565654</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.139678398021317</v>
+        <v>0.4214517467560114</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002453274630056962</v>
+        <v>0.0009026706326364167</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.384476443863938</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.140360212769143</v>
+        <v>0.4217007481040049</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001222682714655666</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.140353684221288</v>
+        <v>0.4216951830483999</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006015507622625393</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.140333295403909</v>
+        <v>0.4216844724855072</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003487911944576901</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.140426131799674</v>
+        <v>0.4217159324561586</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001132944160405111</v>
+        <v>3.963940227943816e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.140303639775085</v>
+        <v>0.4216665958431061</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.339056982904712e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.140299299717237</v>
+        <v>0.421661844344842</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.680054969141058e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.140299677296279</v>
+        <v>0.4216588354730282</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.140293590976268</v>
+        <v>0.4216534489888707</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.140292357785115</v>
+        <v>0.4216500643704199</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.140286022924568</v>
+        <v>0.4216443969401461</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.140281780314414</v>
+        <v>0.4216447774752038</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.140282008635449</v>
+        <v>0.4216450057962385</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.140282098580099</v>
+        <v>0.4216450957408885</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.140281240646514</v>
+        <v>0.4216442378073036</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.140281468967549</v>
+        <v>0.4216444661283383</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.140280673303337</v>
+        <v>0.4216436704641267</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.14028073557271</v>
+        <v>0.4216437327334997</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.140280763247987</v>
+        <v>0.4216437604087766</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.14028091546201</v>
+        <v>0.4216439126227999</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.140280569521049</v>
+        <v>0.4216435666818381</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.14028064562806</v>
+        <v>0.4216436427888497</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.140280811679722</v>
+        <v>0.4216438088405114</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.140281171458322</v>
+        <v>0.4216441686191114</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.14028119221478</v>
+        <v>0.4216441893755691</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.140281295997068</v>
+        <v>0.4216442931578576</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.382453332183273</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.140281524318103</v>
+        <v>0.4216445214788923</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.140281399779357</v>
+        <v>0.4216443969401461</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.140281427454634</v>
+        <v>0.421644424615423</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.140281482805187</v>
+        <v>0.4216444799659769</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.140281745720318</v>
+        <v>0.4216447428811076</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.140281662694487</v>
+        <v>0.4216446598552768</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.14028145512991</v>
+        <v>0.4216444522907</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.140281468967549</v>
+        <v>0.4216444661283383</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.140281607343933</v>
+        <v>0.4216446045047231</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.140281323672345</v>
+        <v>0.4216443208331345</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.140281150701864</v>
+        <v>0.4216441478626537</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.140281046919576</v>
+        <v>0.4216440440803652</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.14028119221478</v>
+        <v>0.4216441893755691</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.140281434373453</v>
+        <v>0.4216444315342424</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.382453332183273</v>
+        <v>0.4279679992113872</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.140281261402972</v>
+        <v>0.4216442585637614</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.384476443863938</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.140280963893745</v>
+        <v>0.4216439610545344</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-3.171991106271274</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.140280950056106</v>
+        <v>0.4216439472168959</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.140280583358687</v>
+        <v>0.4216435805194766</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.140280583358687</v>
+        <v>0.4216435805194766</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.140280521089314</v>
+        <v>0.4216435182501036</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.140280417307025</v>
+        <v>0.4216434144678151</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.382453332183273</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.140280244336545</v>
+        <v>0.4216432414973343</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.140280292768279</v>
+        <v>0.4216432899290689</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.140279932989679</v>
+        <v>0.4216429301504688</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.140279891476764</v>
+        <v>0.4216428886375534</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.140279946827317</v>
+        <v>0.4216429439881071</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.140280002177872</v>
+        <v>0.4216429993386611</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.571991106271275</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.140280043690787</v>
+        <v>0.4216430408515765</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.140279773856837</v>
+        <v>0.4216427710176264</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.140279829207391</v>
+        <v>0.4216428263681803</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.140279974502595</v>
+        <v>0.4216429716633842</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.140279939908498</v>
+        <v>0.421642937069288</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.14027992607086</v>
+        <v>0.4216429232316494</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.14028001601551</v>
+        <v>0.4216430131762997</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9824533321832729</v>
+        <v>-0.184476443863938</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.140280334281194</v>
+        <v>0.4216433314419843</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.140280154391895</v>
+        <v>0.4216431515526841</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-3.171991106271274</v>
+        <v>-2.009365330014588</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.14028019590481</v>
+        <v>0.4216431930655996</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-3.171991106271274</v>
+        <v>-2.009365330014588</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.140280009096691</v>
+        <v>0.4216430062574802</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-3.171991106271274</v>
+        <v>-1.196920886939263</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.140280078284883</v>
+        <v>0.4216430754456728</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.382453332183273</v>
+        <v>-0.3844764438639381</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.140279877639126</v>
+        <v>0.4216428747999149</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.140279919152041</v>
+        <v>0.4216429163128303</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9824533321832729</v>
+        <v>0.6279679992113872</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.140279946827317</v>
+        <v>0.4216429439881071</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.03130587562918663</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01935963705182076</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01825814321637154</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01590543612837791</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001724697649478912</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01335879787802696</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01494381204247475</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0086967833340168</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007905442267656326</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003245986998081207</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01782847568392754</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3844764438639381</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.02135096117854118</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.02219618484377861</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01305096223950386</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01562711223959923</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01850118115544319</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.02440428361296654</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01979432627558708</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01480383053421974</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01090263202786446</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.004075746983289719</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01932809129357338</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01834030821919441</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01987927034497261</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0126868300139904</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.04804873839020729</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3844764438639381</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002993259578943253</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01069964468479156</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.009365330014588</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.006846208125352859</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01260798797011375</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.008020978420972824</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01478993520140648</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02375137433409691</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.006602127104997635</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.002052798867225647</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0001766085624694824</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.008595306426286697</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.001438558101654053</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.003629829734563828</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002175319939851761</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01276564225554466</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01735449954867363</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.008535522967576981</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.196920886939263</v>
+        <v>0.16</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-0.000118366278514266</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.15234641027499</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01995000243186951</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.009365330014588</v>
+        <v>0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.3049815551255529</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.03518314527081071</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03280236199498177</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.196920886939263</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0229177288711071</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3844764438639381</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.02045996114611626</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3844764438639381</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-6.759903522219975e-05</v>
+        <v>0.116891774135733</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.20767885579996</v>
+        <v>0.4704318564228797</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.02031306177377701</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4157036497069443</v>
+        <v>1.058692226760694</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0397369469071638</v>
+        <v>0.09001183506329545</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02326760813593864</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.196920886939263</v>
+        <v>0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2871957454408463</v>
+        <v>0.7675975372350724</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.06960303108402328</v>
+        <v>0.1576640481271645</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.00398670881986618</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3866846507943839</v>
+        <v>0.9929583570149164</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03811715271737443</v>
+        <v>0.08634280850505344</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0123378224670887</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3932559730507666</v>
+        <v>1.007843593566374</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01574293918332445</v>
+        <v>0.03566064053637859</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02113468572497368</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3865846570162738</v>
+        <v>0.9927319459536509</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01961484167448919</v>
+        <v>0.0444300979183424</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.006596114486455917</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4100736500071681</v>
+        <v>1.04593807483244</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01180953426079297</v>
+        <v>0.02675265808772673</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0241101048886776</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4140657003616435</v>
+        <v>1.0549833435075</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.00897624121768067</v>
+        <v>0.02034011003509478</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01028250530362129</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4202064088120279</v>
+        <v>1.068898292062197</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003968230163905284</v>
+        <v>0.008993571675212688</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.02771222218871117</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4191584950322642</v>
+        <v>1.066531093369212</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003147764766567189</v>
+        <v>0.007135381643321368</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01435544714331627</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4214846500149544</v>
+        <v>1.071806627214605</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001558425164565654</v>
+        <v>0.003537096052839946</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0263294018805027</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4214517467560114</v>
+        <v>1.071738409591144</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0009026706326364167</v>
+        <v>0.002054714127905715</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01091564819216728</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.384476443863938</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4217007481040049</v>
+        <v>1.072308870941985</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004488353163182084</v>
+        <v>0.001024857063952857</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00209793820977211</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4216951830483999</v>
+        <v>1.07230258870042</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002192225566657728</v>
+        <v>0.0005038127247415613</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01281097903847694</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4216844724855072</v>
+        <v>1.072284708617381</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001251684583382067</v>
+        <v>0.0002887134444554408</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.00351831316947937</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4217159324561586</v>
+        <v>1.072361394846452</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.963940227943816e-05</v>
+        <v>9.320668501476395e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.00880860909819603</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4216665958431061</v>
+        <v>1.072257747286659</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.745791147271043e-05</v>
+        <v>4.440740523996295e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01589001342654228</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.421661844344842</v>
+        <v>1.072253307828117</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.230980650542531e-06</v>
+        <v>2.190815743119357e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.006994936615228653</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4216588354730282</v>
+        <v>1.072252888955884</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>9.221082681779568e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.02791495993733406</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4216534489888707</v>
+        <v>1.072246957824446</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.008333947509527206</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4216500643704199</v>
+        <v>1.072245184965393</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.02023627981543541</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4216443969401461</v>
+        <v>1.072239185431797</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02857926115393639</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4216447774752038</v>
+        <v>1.072234942821643</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.009504120796918869</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3844764438639381</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4216450057962385</v>
+        <v>1.072235171142677</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003509990870952606</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4216450957408885</v>
+        <v>1.072235261087327</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.00755034014582634</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4216442378073036</v>
+        <v>1.072234403153743</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0003010965883731842</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4216444661283383</v>
+        <v>1.072234631474777</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001581933349370956</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4216436704641267</v>
+        <v>1.072233835810565</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0008733607828617096</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4216437327334997</v>
+        <v>1.072233898079938</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01277762278914452</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4216437604087766</v>
+        <v>1.072233925755215</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01043945923447609</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4216439126227999</v>
+        <v>1.072234077969239</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.008333932608366013</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4216435666818381</v>
+        <v>1.072233732028277</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02196122333407402</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4216436427888497</v>
+        <v>1.072233808135288</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.004344303160905838</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4216438088405114</v>
+        <v>1.07223397418695</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01218675449490547</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4216441686191114</v>
+        <v>1.07223433396555</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01349459961056709</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4216441893755691</v>
+        <v>1.072234354722008</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0248914547264576</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4216442931578576</v>
+        <v>1.072234458504296</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01113223657011986</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4216445214788923</v>
+        <v>1.072234686825331</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01465152576565742</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4216443969401461</v>
+        <v>1.072234562286585</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.00984477624297142</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.421644424615423</v>
+        <v>1.072234589961862</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02372206375002861</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4216444799659769</v>
+        <v>1.072234645312416</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0008963271975517273</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4216447428811076</v>
+        <v>1.072234908227546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.004958499222993851</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4216446598552768</v>
+        <v>1.072234825201716</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01304170116782188</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4216444522907</v>
+        <v>1.072234617637139</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01369248703122139</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4216444661283383</v>
+        <v>1.072234631474777</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.007197108119726181</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4216446045047231</v>
+        <v>1.072234769851162</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002893421798944473</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4216443208331345</v>
+        <v>1.072234486179573</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007503185421228409</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4216441478626537</v>
+        <v>1.072234313209093</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0233827643096447</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4216440440803652</v>
+        <v>1.072234209426804</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01638680323958397</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4216441893755691</v>
+        <v>1.072234354722008</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.00798504427075386</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4279679992113872</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4216444315342424</v>
+        <v>1.072234596880681</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.002515505999326706</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.4279679992113872</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4216442585637614</v>
+        <v>1.0722344239102</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.00747000053524971</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.384476443863938</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4216439610545344</v>
+        <v>1.072234126400973</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003676701337099075</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4216439472168959</v>
+        <v>1.072234112563335</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.004682082682847977</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4216435805194766</v>
+        <v>1.072233745865915</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0159442238509655</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4216435805194766</v>
+        <v>1.072233745865915</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006144952028989792</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4216435182501036</v>
+        <v>1.072233683596542</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003327548503875732</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4216434144678151</v>
+        <v>1.072233579814254</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.007667649537324905</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4216432414973343</v>
+        <v>1.072233406843773</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006473783403635025</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4216432899290689</v>
+        <v>1.072233455275508</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005211744457483292</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4216429301504688</v>
+        <v>1.072233095496908</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005703385919332504</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4216428886375534</v>
+        <v>1.072233053983992</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.006356712430715561</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4216429439881071</v>
+        <v>1.072233109334546</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0007284246385097504</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4216429993386611</v>
+        <v>1.0722331646851</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00226123258471489</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4216430408515765</v>
+        <v>1.072233206198015</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001713927835226059</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.184476443863938</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4216427710176264</v>
+        <v>1.072232936364065</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01280276104807854</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4216428263681803</v>
+        <v>1.072232991714619</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0008351169526576996</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4216429716633842</v>
+        <v>1.072233137009823</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.007929664105176926</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.421642937069288</v>
+        <v>1.072233102415727</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.001449164003133774</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4216429232316494</v>
+        <v>1.072233088578088</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02144232019782066</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4216430131762997</v>
+        <v>1.072233178522738</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01869271323084831</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.184476443863938</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4216433314419843</v>
+        <v>1.072233496788423</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01077523827552795</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.196920886939263</v>
+        <v>0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4216431515526841</v>
+        <v>1.072233316899123</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.009351290762424469</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.009365330014588</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4216431930655996</v>
+        <v>1.072233358412038</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.000378631055355072</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.009365330014588</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4216430062574802</v>
+        <v>1.072233171603919</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005140054970979691</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.196920886939263</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4216430754456728</v>
+        <v>1.072233240792112</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>6.464496254920959e-05</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3844764438639381</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4216428747999149</v>
+        <v>1.072233040146354</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0007491074502468109</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6279679992113872</v>
+        <v>-0.4399999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4216429163128303</v>
+        <v>1.072233081659269</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.008584264665842056</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6279679992113872</v>
+        <v>0.4400000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4216429439881071</v>
+        <v>1.072233109334546</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000006.xlsx
@@ -51824,7 +51824,7 @@
         <v>0.00880860909819603</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>1.072257747286659</v>
@@ -52619,7 +52619,7 @@
         <v>0.01589001342654228</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
         <v>1.072253307828117</v>
@@ -53414,7 +53414,7 @@
         <v>0.006994936615228653</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1600000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>1.072252888955884</v>
@@ -54209,7 +54209,7 @@
         <v>0.02791495993733406</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>1.072246957824446</v>
@@ -55004,7 +55004,7 @@
         <v>0.008333947509527206</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>1.072245184965393</v>
@@ -57389,7 +57389,7 @@
         <v>0.009504120796918869</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.16</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>1.072235171142677</v>
